--- a/41/food/2026-01-15-sm.xlsx
+++ b/41/food/2026-01-15-sm.xlsx
@@ -860,7 +860,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>15.01.2026</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
           <t>Завтрак</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>гор.блюдо</t>
         </is>
@@ -1135,7 +1135,7 @@
           <t>Обед</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>закуска</t>
         </is>
